--- a/Formulário de Report Semanal_ Performance de Afiliados.xlsx
+++ b/Formulário de Report Semanal_ Performance de Afiliados.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -52,6 +52,12 @@
     <t>Qual é a principal ação de incentivo ou campanha desenhada para a próxima semana?</t>
   </si>
   <si>
+    <t>Ações da semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ações Futuras </t>
+  </si>
+  <si>
     <t>Manu Moura</t>
   </si>
   <si>
@@ -77,9 +83,6 @@
   </si>
   <si>
     <t>TTS 🎬 - MCN</t>
-  </si>
-  <si>
-    <t>Não tem como ver pelo Partners</t>
   </si>
   <si>
     <t xml:space="preserve">Ferramenta/ Cozinha/ Projetor </t>
@@ -109,15 +112,56 @@
   </si>
   <si>
     <t>Multi</t>
+  </si>
+  <si>
+    <t>Grazielle Rocha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave de Impacto/ Maquina de solda Inversora / Bateria Compressor de Carro/ Motosserra/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de parceria com fornecedores de ferramentas </t>
+  </si>
+  <si>
+    <t>Parceria com lojas que investem em GMV MAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrada dos Creators na Community </t>
+  </si>
+  <si>
+    <t>Foco na divulgação da Community 300 PRO</t>
+  </si>
+  <si>
+    <t>7/6/0006</t>
+  </si>
+  <si>
+    <t>H&amp;I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">em breve live </t>
+  </si>
+  <si>
+    <t>Ampliar as postagens de links da turma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vai começar live, está gerando ansiedade. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">buscar mais   gente para a lita de liberação de live 
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="[$R$ -416]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy hh:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -146,13 +190,16 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -163,6 +210,9 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -178,6 +228,12 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -259,8 +315,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M5" displayName="Form_Responses" name="Form_Responses" id="1">
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O8" displayName="Form_Responses" name="Form_Responses" id="1">
+  <tableColumns count="15">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="👤 Identificação - Nome do Analista" id="2"/>
     <tableColumn name="Data do Report" id="3"/>
@@ -274,6 +330,8 @@
     <tableColumn name="Principais Ofensores ou Oportunidades" id="11"/>
     <tableColumn name="Qual é o principal gargalo operacional que a agência enfrenta hoje para escalar esses canais?" id="12"/>
     <tableColumn name="Qual é a principal ação de incentivo ou campanha desenhada para a próxima semana?" id="13"/>
+    <tableColumn name="Ações da semana" id="14"/>
+    <tableColumn name="Ações Futuras " id="15"/>
   </tableColumns>
   <tableStyleInfo name="Respostas ao formulário 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -489,7 +547,7 @@
     <col customWidth="1" min="9" max="10" width="37.63"/>
     <col customWidth="1" min="11" max="11" width="33.75"/>
     <col customWidth="1" min="12" max="13" width="37.63"/>
-    <col customWidth="1" min="14" max="19" width="18.88"/>
+    <col customWidth="1" min="14" max="21" width="18.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -532,157 +590,289 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>46199.60802159722</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="5">
         <v>46199.0</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="6">
         <v>64290.0</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="4">
         <v>141.0</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="4">
         <v>56.0</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="3">
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="4">
         <v>3.0</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>46199.647290023146</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="5">
         <v>46199.0</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="5">
-        <v>4560687.16</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="6">
+        <v>5435537.43</v>
+      </c>
+      <c r="F3" s="4">
         <v>240.0</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="3">
+      <c r="G3" s="4">
+        <v>236.0</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="4">
         <v>21.0</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="4">
         <v>33.0</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>46201.49426734954</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="5">
         <v>46201.0</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="5">
-        <v>2.0691048E7</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1305.0</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="6">
+        <v>2.3327616E7</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1513.0</v>
+      </c>
+      <c r="G4" s="4">
         <v>1100.0</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="3">
+      <c r="H4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="4">
         <v>11.0</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="4">
         <v>0.0</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="K4" s="8"/>
+      <c r="L4" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="M4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>46202.588164444445</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="B5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="11">
         <v>46202.0</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="12">
+        <v>81674.34</v>
+      </c>
+      <c r="F5" s="10">
+        <v>233.0</v>
+      </c>
+      <c r="G5" s="10">
+        <v>192.0</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="10">
+        <v>21.0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>33.0</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="9">
+        <v>46206.73771255787</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="11">
+        <v>46206.0</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="12">
+        <v>158990.39</v>
+      </c>
+      <c r="F6" s="10">
+        <v>246.0</v>
+      </c>
+      <c r="G6" s="10">
+        <v>117.0</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="10">
+        <v>15.0</v>
+      </c>
+      <c r="J6" s="10">
+        <v>30.0</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="9">
+        <v>46209.41234232639</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="12">
+        <v>79610.0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>353.0</v>
+      </c>
+      <c r="G7" s="10">
+        <v>60.0</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="14">
+        <v>46209.38927083334</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="10">
-        <v>75174.1</v>
-      </c>
-      <c r="F5" s="8">
-        <v>233.0</v>
-      </c>
-      <c r="G5" s="8">
-        <v>183.0</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="C8" s="11">
+        <v>46209.0</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="8">
+      <c r="E8" s="12">
+        <v>6106.9</v>
+      </c>
+      <c r="F8" s="10">
+        <v>246.0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>56.0</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="10">
         <v>21.0</v>
-      </c>
-      <c r="J5" s="8">
-        <v>33.0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:E5">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:E8">
       <formula1>AND(ISNUMBER(E2),(NOT(OR(NOT(ISERROR(DATEVALUE(E2))), AND(ISNUMBER(E2), LEFT(CELL("format", E2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>

--- a/Formulário de Report Semanal_ Performance de Afiliados.xlsx
+++ b/Formulário de Report Semanal_ Performance de Afiliados.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>Foco na divulgação da Community 300 PRO</t>
-  </si>
-  <si>
-    <t>7/6/0006</t>
   </si>
   <si>
     <t>H&amp;I</t>
@@ -224,10 +221,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -605,7 +602,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="5">
-        <v>46199.0</v>
+        <v>46201.0</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>16</v>
@@ -648,7 +645,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="5">
-        <v>46199.0</v>
+        <v>46201.0</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>23</v>
@@ -725,13 +722,13 @@
       <c r="B5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="11">
-        <v>46202.0</v>
+      <c r="C5" s="5">
+        <v>46201.0</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>81674.34</v>
       </c>
       <c r="F5" s="10">
@@ -757,13 +754,13 @@
       <c r="B6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="11">
-        <v>46206.0</v>
+      <c r="C6" s="12">
+        <v>46209.0</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>158990.39</v>
       </c>
       <c r="F6" s="10">
@@ -801,13 +798,13 @@
       <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>39</v>
+      <c r="C7" s="12">
+        <v>46209.0</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>79610.0</v>
       </c>
       <c r="F7" s="10">
@@ -817,7 +814,7 @@
         <v>60.0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="10">
         <v>4.0</v>
@@ -826,19 +823,19 @@
         <v>0.0</v>
       </c>
       <c r="K7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="M7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="N7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="O7" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
@@ -848,13 +845,13 @@
       <c r="B8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="12">
         <v>46209.0</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>6106.9</v>
       </c>
       <c r="F8" s="10">

--- a/Formulário de Report Semanal_ Performance de Afiliados.xlsx
+++ b/Formulário de Report Semanal_ Performance de Afiliados.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -147,8 +147,31 @@
     <t xml:space="preserve">7.7 </t>
   </si>
   <si>
-    <t xml:space="preserve">buscar mais   gente para a lita de liberação de live 
+    <t xml:space="preserve">buscar mais  gente para a lita de liberação de live 
 </t>
+  </si>
+  <si>
+    <t>Maza</t>
+  </si>
+  <si>
+    <t>https://shopee.com.br/product/1024829312/23493492803
+https://shopee.com.br/product/432843460/19198648197
+https://shopee.com.br/product/1007831167/52310130382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COmunicação mais assertiva, </t>
+  </si>
+  <si>
+    <t>Apoio no Planejamento estratégico, suporte</t>
+  </si>
+  <si>
+    <t>Meta 1 Milhão, precisamos disso pra (ontem)</t>
+  </si>
+  <si>
+    <t>Foco nas campanhas e ações para o 7,7, Entrada nova recrutadora Brenda</t>
+  </si>
+  <si>
+    <t>Lives de recrutamento semanais, treinamentos e açoes de incentivo para crescimento</t>
   </si>
 </sst>
 </file>
@@ -312,7 +335,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O8" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O9" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="15">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="👤 Identificação - Nome do Analista" id="2"/>
@@ -544,7 +567,8 @@
     <col customWidth="1" min="9" max="10" width="37.63"/>
     <col customWidth="1" min="11" max="11" width="33.75"/>
     <col customWidth="1" min="12" max="13" width="37.63"/>
-    <col customWidth="1" min="14" max="21" width="18.88"/>
+    <col customWidth="1" min="14" max="14" width="23.75"/>
+    <col customWidth="1" min="15" max="21" width="18.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -608,7 +632,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="6">
-        <v>64290.0</v>
+        <v>79610.0</v>
       </c>
       <c r="F2" s="4">
         <v>141.0</v>
@@ -805,7 +829,7 @@
         <v>16</v>
       </c>
       <c r="E7" s="11">
-        <v>79610.0</v>
+        <v>11620.0</v>
       </c>
       <c r="F7" s="10">
         <v>353.0</v>
@@ -839,37 +863,84 @@
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="14">
-        <v>46209.38927083334</v>
+      <c r="A8" s="9">
+        <v>46209.44481056713</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C8" s="12">
         <v>46209.0</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="11">
+        <v>3096016.0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1520.0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1300.0</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="10">
+        <v>18.0</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="14">
+        <v>46209.38927083334</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="12">
+        <v>46209.0</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E9" s="11">
         <v>6106.9</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F9" s="10">
         <v>246.0</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G9" s="10">
         <v>56.0</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I9" s="10">
         <v>21.0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:E8">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:E9">
       <formula1>AND(ISNUMBER(E2),(NOT(OR(NOT(ISERROR(DATEVALUE(E2))), AND(ISNUMBER(E2), LEFT(CELL("format", E2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>

--- a/Formulário de Report Semanal_ Performance de Afiliados.xlsx
+++ b/Formulário de Report Semanal_ Performance de Afiliados.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -172,6 +172,51 @@
   </si>
   <si>
     <t>Lives de recrutamento semanais, treinamentos e açoes de incentivo para crescimento</t>
+  </si>
+  <si>
+    <t>Grazielle F B Rocha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Chave de Impacto 48V / Conjunto de ferramentas 4 em 1/ Máquina de solda inversora MMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queda nas lives e vídeos pós ataque de hater referente ao mês de Junho. Devido ao grande número de bloqueios em live as contas floparam. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parceria com fornecedores específicos, Moda vestuário F M e ferramentas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acompanhar a campanha alumínio de perto </t>
+  </si>
+  <si>
+    <t>https://shopee.com.br/product/1024829312/23493492803
+https://shopee.com.br/product/1006215031/26535612680
+https://shopee.com.br/product/432843460/19198648197</t>
+  </si>
+  <si>
+    <t>Mudancças nas politicas da shopee, oportunidade de criar conteudo e trazer mais criadores (em andamento)</t>
+  </si>
+  <si>
+    <t>o mesmo</t>
+  </si>
+  <si>
+    <t>Operação 1 Milhão, treinamento shopee videos na sexta feira</t>
+  </si>
+  <si>
+    <t>Treinamento ao vivo - Melhores praticas para shopee video - sexta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H&amp;I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lentidão do  mercado livre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">meta-interna de fechamento </t>
+  </si>
+  <si>
+    <t>ativação de novatos</t>
   </si>
 </sst>
 </file>
@@ -210,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -251,6 +296,9 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -335,7 +383,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O9" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O13" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="15">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="👤 Identificação - Nome do Analista" id="2"/>
@@ -910,37 +958,195 @@
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="14">
+      <c r="A9" s="9">
+        <v>46214.57967516204</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="12">
+        <v>46214.0</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="11">
+        <v>1471385.22</v>
+      </c>
+      <c r="F9" s="10">
+        <v>249.0</v>
+      </c>
+      <c r="G9" s="10">
+        <v>169.0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="10">
+        <v>25.0</v>
+      </c>
+      <c r="J9" s="10">
+        <v>47.0</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="9">
+        <v>46214.57967516204</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="12">
+        <v>46214.0</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="11">
+        <v>1.2908927E7</v>
+      </c>
+      <c r="F10" s="14">
+        <v>1822.0</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1600.0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="10">
+        <v>18.0</v>
+      </c>
+      <c r="J10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="9">
+        <v>46214.57967516204</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="12">
+        <v>46214.0</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="11">
+        <v>37172.0</v>
+      </c>
+      <c r="F11" s="10">
+        <v>363.0</v>
+      </c>
+      <c r="G11" s="10">
+        <v>45.0</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="15">
         <v>46209.38927083334</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C12" s="12">
         <v>46209.0</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E12" s="11">
         <v>6106.9</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F12" s="10">
         <v>246.0</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G12" s="10">
         <v>56.0</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I12" s="10">
         <v>21.0</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="9">
+        <v>46214.57967516204</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="12">
+        <v>46214.0</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="11">
+        <v>16238.47</v>
+      </c>
+      <c r="F13" s="10">
+        <v>246.0</v>
+      </c>
+      <c r="G13" s="10">
+        <v>89.0</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="10">
+        <v>105.0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:E9">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2:E13">
       <formula1>AND(ISNUMBER(E2),(NOT(OR(NOT(ISERROR(DATEVALUE(E2))), AND(ISNUMBER(E2), LEFT(CELL("format", E2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
